--- a/data/trans_dic/P36B08_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,36; 67,31</t>
+          <t>61,04; 66,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,19; 76,07</t>
+          <t>69,71; 75,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,64; 79,71</t>
+          <t>73,4; 79,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,21; 94,63</t>
+          <t>91,28; 95,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,5; 75,36</t>
+          <t>70,53; 75,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,24; 82,73</t>
+          <t>78,36; 82,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,2; 81,86</t>
+          <t>76,64; 82,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,23; 95,72</t>
+          <t>93,43; 95,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,93; 70,73</t>
+          <t>67,28; 70,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75,74; 79,22</t>
+          <t>75,4; 79,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,04; 80,22</t>
+          <t>75,91; 79,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,49; 94,89</t>
+          <t>93,02; 95,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,13; 64,13</t>
+          <t>59,24; 64,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,11; 71,59</t>
+          <t>67,07; 71,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,19; 71,31</t>
+          <t>67,02; 71,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,43; 95,76</t>
+          <t>92,5; 94,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,31; 71,97</t>
+          <t>67,35; 72,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,34; 79,32</t>
+          <t>75,37; 79,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,0; 76,96</t>
+          <t>73,13; 76,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,96; 97,27</t>
+          <t>94,9; 96,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,72; 67,15</t>
+          <t>63,93; 67,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71,63; 74,7</t>
+          <t>71,48; 74,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,53; 73,52</t>
+          <t>70,6; 73,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,08; 96,17</t>
+          <t>93,96; 95,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,63; 70,12</t>
+          <t>61,84; 70,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,3; 79,3</t>
+          <t>71,33; 79,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,53; 81,94</t>
+          <t>73,57; 81,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95,27; 98,19</t>
+          <t>94,95; 97,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,77; 74,53</t>
+          <t>66,36; 74,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,14; 88,2</t>
+          <t>81,4; 88,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,47; 85,08</t>
+          <t>78,36; 84,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94,65; 97,83</t>
+          <t>94,9; 97,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,69; 71,23</t>
+          <t>65,59; 71,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77,13; 82,67</t>
+          <t>77,13; 82,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,7; 82,38</t>
+          <t>77,48; 82,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95,43; 97,65</t>
+          <t>95,54; 97,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,48; 64,97</t>
+          <t>61,68; 64,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,57; 72,87</t>
+          <t>69,4; 72,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,83; 73,85</t>
+          <t>70,71; 73,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,35; 95,79</t>
+          <t>93,51; 95,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,3; 72,52</t>
+          <t>69,41; 72,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,12; 80,86</t>
+          <t>78,22; 80,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,94; 78,88</t>
+          <t>75,99; 78,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,07; 96,7</t>
+          <t>95,12; 96,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,1; 68,46</t>
+          <t>65,9; 68,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,35; 76,44</t>
+          <t>74,37; 76,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,73; 75,95</t>
+          <t>73,72; 75,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,54; 95,98</t>
+          <t>94,51; 95,65</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>477259</t>
+          <t>539690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>712521</t>
+          <t>776408</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1189780</t>
+          <t>1316098</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>632592; 693891</t>
+          <t>629252; 689821</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>681248; 738293</t>
+          <t>676509; 735193</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>554045; 599698</t>
+          <t>552266; 595816</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>463841; 486565</t>
+          <t>527395; 550379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>927218; 991006</t>
+          <t>927572; 991585</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1046749; 1106793</t>
+          <t>1048308; 1107819</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>754561; 810544</t>
+          <t>758893; 812431</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>702458; 721257</t>
+          <t>766077; 785593</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1570150; 1659357</t>
+          <t>1578313; 1660859</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1748309; 1828635</t>
+          <t>1740562; 1828567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1325055; 1397818</t>
+          <t>1322716; 1392991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1172509; 1202934</t>
+          <t>1300245; 1332032</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2152873</t>
+          <t>2090869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2150753</t>
+          <t>2080003</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4303625</t>
+          <t>4170873</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1001336; 1085929</t>
+          <t>1003160; 1088077</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1316583; 1404547</t>
+          <t>1315939; 1398879</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1386213; 1471325</t>
+          <t>1382707; 1469026</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2114643; 2190775</t>
+          <t>2060569; 2115548</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1067980; 1141910</t>
+          <t>1068601; 1142314</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1318318; 1387984</t>
+          <t>1318870; 1387499</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1443901; 1522177</t>
+          <t>1446583; 1522904</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2123352; 2175007</t>
+          <t>2058745; 2096954</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2090159; 2202396</t>
+          <t>2096917; 2207928</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2658925; 2772696</t>
+          <t>2653359; 2767576</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2850275; 2970913</t>
+          <t>2853009; 2972825</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4255908; 4350261</t>
+          <t>4131480; 4201549</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626623</t>
+          <t>688398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>637879</t>
+          <t>710243</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1264502</t>
+          <t>1398642</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>339807; 386661</t>
+          <t>340996; 387595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>342365; 380764</t>
+          <t>342487; 380212</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>406087; 446468</t>
+          <t>400867; 443869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>616032; 634935</t>
+          <t>675666; 696954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>318117; 355086</t>
+          <t>316132; 355132</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>370572; 402788</t>
+          <t>371738; 403255</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>429362; 465530</t>
+          <t>428757; 464831</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>625116; 646109</t>
+          <t>697393; 718482</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>675218; 732074</t>
+          <t>674115; 733612</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>722630; 774524</t>
+          <t>722561; 772652</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>848537; 899600</t>
+          <t>846088; 900114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1247349; 1276375</t>
+          <t>1381989; 1411211</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3256754</t>
+          <t>3318956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3501153</t>
+          <t>3566656</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6757907</t>
+          <t>6885612</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2013745; 2128375</t>
+          <t>2020508; 2125928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2374169; 2486711</t>
+          <t>2368457; 2478583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2380244; 2481746</t>
+          <t>2376037; 2482404</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3219165; 3303552</t>
+          <t>3288790; 3352335</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2341215; 2449848</t>
+          <t>2344836; 2451375</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2769034; 2865902</t>
+          <t>2772587; 2868163</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2669424; 2772842</t>
+          <t>2671238; 2769068</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3470106; 3529424</t>
+          <t>3542537; 3590680</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4397999; 4555090</t>
+          <t>4385114; 4542259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5172303; 5318060</t>
+          <t>5174131; 5329196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5069478; 5222110</t>
+          <t>5069034; 5220895</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6711121; 6813273</t>
+          <t>6843790; 6926527</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B08_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
